--- a/naver-place-crawler/results_health/제주_PT.xlsx
+++ b/naver-place-crawler/results_health/제주_PT.xlsx
@@ -426,13 +426,13 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="7" max="7"/>
     <col width="42" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="35" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -581,7 +581,7 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>제주 제주시 구남동8길 58 올레마트 2층 정글짐</t>
+          <t>제주특별자치도 제주시 구남동8길 58 올레마트 2층 정글짐</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -658,29 +658,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>마인드휘트니스 중앙점</t>
+          <t>사람휘트니스 이도7호점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>mindfitness23@naver.com</t>
+          <t>saram_ido@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1468-2371</t>
+          <t>0507-1404-1264</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>제주 제주시 중앙로 53 JJ아트뷰타워 3, 4층</t>
+          <t>제주특별자치도 제주시 연삼로 424</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/mindfitness23</t>
+          <t>https://blog.naver.com/saram_ido</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -700,14 +700,10 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wo03pkw</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -719,13 +715,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1532</v>
+        <v>272</v>
       </c>
       <c r="Q3" t="n">
-        <v>539</v>
+        <v>461</v>
       </c>
       <c r="R3" t="n">
-        <v>2071</v>
+        <v>733</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -734,12 +730,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1840405943</t>
+          <t>1089331988</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1840405943</t>
+          <t>https://m.place.naver.com/place/1089331988</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -756,39 +752,39 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>마인드휘트니스 인제점</t>
+          <t>마인드휘트니스 중앙점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>mindfitness10@naver.com</t>
+          <t>mindfitness23@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1346-0791</t>
+          <t>0507-1468-2371</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>제주 제주시 동광로 105 1,2,3층</t>
+          <t>제주특별자치도 제주시 중앙로 53 JJ아트뷰타워 3, 4층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://www.mindfitness-official.com</t>
+          <t>https://blog.naver.com/mindfitness23</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -798,17 +794,13 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4ki45</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -817,13 +809,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>651</v>
+        <v>1532</v>
       </c>
       <c r="Q4" t="n">
-        <v>795</v>
+        <v>539</v>
       </c>
       <c r="R4" t="n">
-        <v>1446</v>
+        <v>2071</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -832,12 +824,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1884516770</t>
+          <t>1840405943</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1884516770</t>
+          <t>https://m.place.naver.com/place/1840405943</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -854,39 +846,39 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>마인드휘트니스 PT&amp;필라테스 터미널점</t>
+          <t>마인드휘트니스 인제점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>mindfitness5@naver.com</t>
+          <t>mindfitness10@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1302-0795</t>
+          <t>0507-1346-0791</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>제주 제주시 서광로 167 3층 마인드휘트니스</t>
+          <t>제주특별자치도 제주시 동광로 105 1,2,3층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/mindfitness5</t>
+          <t>https://www.mindfitness-official.com</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -896,17 +888,13 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wcs1gf</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -915,13 +903,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>859</v>
+        <v>651</v>
       </c>
       <c r="Q5" t="n">
-        <v>642</v>
+        <v>794</v>
       </c>
       <c r="R5" t="n">
-        <v>1501</v>
+        <v>1445</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -930,12 +918,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1161375366</t>
+          <t>1884516770</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1161375366</t>
+          <t>https://m.place.naver.com/place/1884516770</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -947,39 +935,39 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>코어스포츠제주 헬스&amp;PT</t>
+          <t>마인드휘트니스 PT&amp;필라테스 터미널점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>core_sport_jeju@naver.com</t>
+          <t>mindfitness5@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1409-1645</t>
+          <t>0507-1302-0795</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>제주 제주시 도령로 64 3층</t>
+          <t>제주특별자치도 제주시 서광로 167 3층 마인드휘트니스</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>http://coresportsjeju.com/</t>
+          <t>https://blog.naver.com/mindfitness5</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -994,14 +982,10 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wrehaip</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -1013,13 +997,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>157</v>
+        <v>861</v>
       </c>
       <c r="Q6" t="n">
-        <v>569</v>
+        <v>642</v>
       </c>
       <c r="R6" t="n">
-        <v>726</v>
+        <v>1503</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1028,12 +1012,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1159226809</t>
+          <t>1161375366</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1159226809</t>
+          <t>https://m.place.naver.com/place/1161375366</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1050,34 +1034,34 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>커스텀짐 한림점</t>
+          <t>코어스포츠제주 헬스&amp;PT</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>customhallim@naver.com</t>
+          <t>core_sport_jeju@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1363-2448</t>
+          <t>0507-1409-1645</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>제주 제주시 한림읍 한림중앙로 61-14</t>
+          <t>제주특별자치도 제주시 도령로 64 3층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/custom_hallim/</t>
+          <t>http://coresportsjeju.com/</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1087,19 +1071,15 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w40eab</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1111,13 +1091,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>749</v>
+        <v>157</v>
       </c>
       <c r="Q7" t="n">
-        <v>169</v>
+        <v>569</v>
       </c>
       <c r="R7" t="n">
-        <v>918</v>
+        <v>726</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1126,12 +1106,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1674334378</t>
+          <t>1159226809</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1674334378</t>
+          <t>https://m.place.naver.com/place/1159226809</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1148,29 +1128,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>팀아지트체형교정pt</t>
+          <t>커스텀짐 한림점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>hyunjsh1@naver.com</t>
+          <t>customhallim@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1410-8050</t>
+          <t>0507-1363-2448</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>제주 제주시 노형9길 9-3 1층 팀아지트</t>
+          <t>제주특별자치도 제주시 한림읍 한림중앙로 61-14</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/hyunjsh1</t>
+          <t>https://www.instagram.com/custom_hallim/</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1185,19 +1165,15 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wc9trv</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
           <t>X</t>
@@ -1209,13 +1185,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>86</v>
+        <v>749</v>
       </c>
       <c r="Q8" t="n">
-        <v>160</v>
+        <v>169</v>
       </c>
       <c r="R8" t="n">
-        <v>246</v>
+        <v>918</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1224,12 +1200,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>35136135</t>
+          <t>1674334378</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/35136135</t>
+          <t>https://m.place.naver.com/place/1674334378</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1246,29 +1222,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>아틀라스&amp;바른자세 운동센터</t>
+          <t>팀아지트체형교정pt</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>atlascs@naver.com</t>
+          <t>hyunjsh1@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1341-0145</t>
+          <t>0507-1410-8050</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>제주 제주시 과천로 31 4층</t>
+          <t>제주특별자치도 제주시 노형9길 9-3 1층 팀아지트</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/jejuatlas/</t>
+          <t>https://blog.naver.com/hyunjsh1</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1283,19 +1259,15 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wcfqcj</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
           <t>X</t>
@@ -1307,13 +1279,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>129</v>
+        <v>86</v>
       </c>
       <c r="Q9" t="n">
-        <v>189</v>
+        <v>160</v>
       </c>
       <c r="R9" t="n">
-        <v>318</v>
+        <v>246</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1322,12 +1294,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>37264400</t>
+          <t>35136135</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37264400</t>
+          <t>https://m.place.naver.com/place/35136135</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1339,34 +1311,34 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>마인드휘트니스 PT&amp;필라테스&amp;요가 동홍점</t>
+          <t>아틀라스&amp;바른자세 운동센터</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>mindfitness7@naver.com</t>
+          <t>atlascs@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1352-0797</t>
+          <t>0507-1341-0145</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>제주 서귀포시 동홍중앙로 55 2층,3층</t>
+          <t>제주특별자치도 제주시 과천로 31 4층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/mindfitness7</t>
+          <t>https://www.instagram.com/jejuatlas/</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1381,19 +1353,15 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4yf5p</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
           <t>X</t>
@@ -1405,13 +1373,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>740</v>
+        <v>129</v>
       </c>
       <c r="Q10" t="n">
-        <v>766</v>
+        <v>189</v>
       </c>
       <c r="R10" t="n">
-        <v>1506</v>
+        <v>318</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1420,12 +1388,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1069617460</t>
+          <t>37264400</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1069617460</t>
+          <t>https://m.place.naver.com/place/37264400</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1442,29 +1410,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>휴메이크휘트니스 이도점</t>
+          <t>마인드휘트니스 PT&amp;필라테스&amp;요가 동홍점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>humake_ido@naver.com</t>
+          <t>mindfitness7@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1355-2179</t>
+          <t>0507-1352-0797</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>제주 제주시 연삼로 411 네오캠퍼스 2층 휴메이크휘트니스 제주이도점</t>
+          <t>제주특별자치도 서귀포시 동홍중앙로 55 2층,3층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/humake_ido</t>
+          <t>https://blog.naver.com/mindfitness7</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1484,14 +1452,10 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/whys2qr</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
           <t>X</t>
@@ -1503,13 +1467,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>611</v>
+        <v>740</v>
       </c>
       <c r="Q11" t="n">
-        <v>140</v>
+        <v>767</v>
       </c>
       <c r="R11" t="n">
-        <v>751</v>
+        <v>1507</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1518,12 +1482,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>965909506</t>
+          <t>1069617460</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/965909506</t>
+          <t>https://m.place.naver.com/place/1069617460</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">

--- a/naver-place-crawler/results_health/제주_PT.xlsx
+++ b/naver-place-crawler/results_health/제주_PT.xlsx
@@ -426,13 +426,13 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="34" customWidth="1" min="7" max="7"/>
+    <col width="33" customWidth="1" min="7" max="7"/>
     <col width="42" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="35" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -581,7 +581,7 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>제주특별자치도 제주시 구남동8길 58 올레마트 2층 정글짐</t>
+          <t>제주 제주시 구남동8길 58 올레마트 2층 정글짐</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -646,7 +646,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -675,7 +675,7 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>제주특별자치도 제주시 연삼로 424</t>
+          <t>제주 제주시 연삼로 424</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -700,10 +700,14 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5yc0j</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -740,7 +744,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -769,7 +773,7 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>제주특별자치도 제주시 중앙로 53 JJ아트뷰타워 3, 4층</t>
+          <t>제주 제주시 중앙로 53 JJ아트뷰타워 3, 4층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -794,10 +798,14 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wo03pkw</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
           <t>X</t>
@@ -809,13 +817,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1532</v>
+        <v>1536</v>
       </c>
       <c r="Q4" t="n">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="R4" t="n">
-        <v>2071</v>
+        <v>2077</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -834,7 +842,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -846,39 +854,39 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>마인드휘트니스 인제점</t>
+          <t>마인드휘트니스 PT&amp;필라테스 터미널점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>mindfitness10@naver.com</t>
+          <t>mindfitness5@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1346-0791</t>
+          <t>0507-1302-0795</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>제주특별자치도 제주시 동광로 105 1,2,3층</t>
+          <t>제주 제주시 서광로 167 3층 마인드휘트니스</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://www.mindfitness-official.com</t>
+          <t>https://blog.naver.com/mindfitness5</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -888,13 +896,17 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wcs1gf</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -903,13 +915,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>651</v>
+        <v>866</v>
       </c>
       <c r="Q5" t="n">
-        <v>794</v>
+        <v>643</v>
       </c>
       <c r="R5" t="n">
-        <v>1445</v>
+        <v>1509</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -918,51 +930,51 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1884516770</t>
+          <t>1161375366</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1884516770</t>
+          <t>https://m.place.naver.com/place/1161375366</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>마인드휘트니스 PT&amp;필라테스 터미널점</t>
+          <t>커스텀짐 한림점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>mindfitness5@naver.com</t>
+          <t>customhallim@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1302-0795</t>
+          <t>0507-1363-2448</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>제주특별자치도 제주시 서광로 167 3층 마인드휘트니스</t>
+          <t>제주 제주시 한림읍 한림중앙로 61-14</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/mindfitness5</t>
+          <t>https://www.instagram.com/custom_hallim/</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -977,15 +989,19 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w40eab</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -997,13 +1013,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>861</v>
+        <v>750</v>
       </c>
       <c r="Q6" t="n">
-        <v>642</v>
+        <v>169</v>
       </c>
       <c r="R6" t="n">
-        <v>1503</v>
+        <v>919</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1012,56 +1028,56 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1161375366</t>
+          <t>1674334378</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1161375366</t>
+          <t>https://m.place.naver.com/place/1674334378</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>코어스포츠제주 헬스&amp;PT</t>
+          <t>마인드휘트니스 제주공항점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>core_sport_jeju@naver.com</t>
+          <t>mindfitness13@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1409-1645</t>
+          <t>0507-1348-0798</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>제주특별자치도 제주시 도령로 64 3층</t>
+          <t>제주 제주시 도령로 167 에이동 2층, 3층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>http://coresportsjeju.com/</t>
+          <t>https://blog.naver.com/mindfitness13</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1076,10 +1092,14 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4ptgx</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1091,13 +1111,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>157</v>
+        <v>2147</v>
       </c>
       <c r="Q7" t="n">
-        <v>569</v>
+        <v>507</v>
       </c>
       <c r="R7" t="n">
-        <v>726</v>
+        <v>2654</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1106,17 +1126,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1159226809</t>
+          <t>1102972683</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1159226809</t>
+          <t>https://m.place.naver.com/place/1102972683</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1128,29 +1148,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>커스텀짐 한림점</t>
+          <t>아틀라스&amp;바른자세 운동센터</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>customhallim@naver.com</t>
+          <t>atlascs@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1363-2448</t>
+          <t>0507-1341-0145</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>제주특별자치도 제주시 한림읍 한림중앙로 61-14</t>
+          <t>제주 제주시 과천로 31 4층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/custom_hallim/</t>
+          <t>https://www.instagram.com/jejuatlas/</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1170,10 +1190,14 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wcfqcj</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr">
         <is>
           <t>X</t>
@@ -1185,13 +1209,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>749</v>
+        <v>129</v>
       </c>
       <c r="Q8" t="n">
-        <v>169</v>
+        <v>188</v>
       </c>
       <c r="R8" t="n">
-        <v>918</v>
+        <v>317</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1200,17 +1224,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1674334378</t>
+          <t>37264400</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1674334378</t>
+          <t>https://m.place.naver.com/place/37264400</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1239,7 +1263,7 @@
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>제주특별자치도 제주시 노형9길 9-3 1층 팀아지트</t>
+          <t>제주 제주시 노형9길 9-3 1층 팀아지트</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1264,10 +1288,14 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wc9trv</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr">
         <is>
           <t>X</t>
@@ -1304,41 +1332,41 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>아틀라스&amp;바른자세 운동센터</t>
+          <t>마인드휘트니스 PT&amp;필라테스&amp;요가 동홍점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>atlascs@naver.com</t>
+          <t>mindfitness7@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1341-0145</t>
+          <t>0507-1352-0797</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>제주특별자치도 제주시 과천로 31 4층</t>
+          <t>제주 서귀포시 동홍중앙로 55 2층,3층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/jejuatlas/</t>
+          <t>https://blog.naver.com/mindfitness7</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1353,15 +1381,19 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4yf5p</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr">
         <is>
           <t>X</t>
@@ -1373,13 +1405,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>129</v>
+        <v>741</v>
       </c>
       <c r="Q10" t="n">
-        <v>189</v>
+        <v>768</v>
       </c>
       <c r="R10" t="n">
-        <v>318</v>
+        <v>1509</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1388,17 +1420,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>37264400</t>
+          <t>1069617460</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37264400</t>
+          <t>https://m.place.naver.com/place/1069617460</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1410,29 +1442,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>마인드휘트니스 PT&amp;필라테스&amp;요가 동홍점</t>
+          <t>마인드휘트니스 노형점 헬스&amp;PT&amp;필라테스</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>mindfitness7@naver.com</t>
+          <t>mindfitness15@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1352-0797</t>
+          <t>0507-1439-0799</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>제주특별자치도 서귀포시 동홍중앙로 55 2층,3층</t>
+          <t>제주 제주시 월랑로 1 8층, 9층 마인드휘트니스 노형점</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/mindfitness7</t>
+          <t>https://blog.naver.com/mindfitness15</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1452,10 +1484,14 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4g2g5</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr">
         <is>
           <t>X</t>
@@ -1467,13 +1503,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>740</v>
+        <v>819</v>
       </c>
       <c r="Q11" t="n">
-        <v>767</v>
+        <v>780</v>
       </c>
       <c r="R11" t="n">
-        <v>1507</v>
+        <v>1599</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1482,17 +1518,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1069617460</t>
+          <t>1485921447</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1069617460</t>
+          <t>https://m.place.naver.com/place/1485921447</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/제주_PT.xlsx
+++ b/naver-place-crawler/results_health/제주_PT.xlsx
@@ -646,7 +646,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -658,29 +658,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>사람휘트니스 이도7호점</t>
+          <t>마인드휘트니스 중앙점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>saram_ido@naver.com</t>
+          <t>mindfitness23@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1404-1264</t>
+          <t>0507-1468-2371</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>제주 제주시 연삼로 424</t>
+          <t>제주 제주시 중앙로 53 JJ아트뷰타워 3, 4층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/saram_ido</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -690,12 +690,12 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -705,7 +705,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5yc0j</t>
+          <t>https://talk.naver.com/ct/wo03pkw</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>272</v>
+        <v>1536</v>
       </c>
       <c r="Q3" t="n">
-        <v>461</v>
+        <v>541</v>
       </c>
       <c r="R3" t="n">
-        <v>733</v>
+        <v>2077</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -734,51 +734,51 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1089331988</t>
+          <t>1840405943</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1089331988</t>
+          <t>https://m.place.naver.com/place/1840405943</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>마인드휘트니스 중앙점</t>
+          <t>커스텀짐 한림점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>mindfitness23@naver.com</t>
+          <t>customhallim@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1468-2371</t>
+          <t>0507-1363-2448</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>제주 제주시 중앙로 53 JJ아트뷰타워 3, 4층</t>
+          <t>제주 제주시 한림읍 한림중앙로 61-14</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/mindfitness23</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -788,12 +788,12 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -803,7 +803,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wo03pkw</t>
+          <t>https://talk.naver.com/ct/w40eab</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1536</v>
+        <v>752</v>
       </c>
       <c r="Q4" t="n">
-        <v>541</v>
+        <v>169</v>
       </c>
       <c r="R4" t="n">
-        <v>2077</v>
+        <v>921</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -832,17 +832,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1840405943</t>
+          <t>1674334378</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1840405943</t>
+          <t>https://m.place.naver.com/place/1674334378</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -854,29 +854,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>마인드휘트니스 PT&amp;필라테스 터미널점</t>
+          <t>마인드휘트니스 제주공항점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>mindfitness5@naver.com</t>
+          <t>mindfitness13@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1302-0795</t>
+          <t>0507-1348-0798</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>제주 제주시 서광로 167 3층 마인드휘트니스</t>
+          <t>제주 제주시 도령로 167 에이동 2층, 3층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/mindfitness5</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -886,12 +886,12 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wcs1gf</t>
+          <t>https://talk.naver.com/ct/w4ptgx</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -915,13 +915,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>866</v>
+        <v>2149</v>
       </c>
       <c r="Q5" t="n">
-        <v>643</v>
+        <v>507</v>
       </c>
       <c r="R5" t="n">
-        <v>1509</v>
+        <v>2656</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -930,17 +930,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1161375366</t>
+          <t>1102972683</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1161375366</t>
+          <t>https://m.place.naver.com/place/1102972683</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -952,29 +952,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>커스텀짐 한림점</t>
+          <t>아틀라스&amp;바른자세 운동센터</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>customhallim@naver.com</t>
+          <t>atlascs@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1363-2448</t>
+          <t>0507-1341-0145</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>제주 제주시 한림읍 한림중앙로 61-14</t>
+          <t>제주 제주시 과천로 31 4층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/custom_hallim/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -999,7 +999,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w40eab</t>
+          <t>https://talk.naver.com/ct/wcfqcj</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1013,13 +1013,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>750</v>
+        <v>129</v>
       </c>
       <c r="Q6" t="n">
-        <v>169</v>
+        <v>188</v>
       </c>
       <c r="R6" t="n">
-        <v>919</v>
+        <v>317</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1028,17 +1028,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1674334378</t>
+          <t>37264400</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1674334378</t>
+          <t>https://m.place.naver.com/place/37264400</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1050,29 +1050,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>마인드휘트니스 제주공항점</t>
+          <t>바름휘트니스 노형점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>mindfitness13@naver.com</t>
+          <t>bareum_fitness@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1348-0798</t>
+          <t>0507-1302-4841</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>제주 제주시 도령로 167 에이동 2층, 3층</t>
+          <t>제주 제주시 원노형로 54 3층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/mindfitness13</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1082,12 +1082,12 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1097,7 +1097,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4ptgx</t>
+          <t>https://talk.naver.com/ct/wfn65t0</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1111,13 +1111,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>2147</v>
+        <v>395</v>
       </c>
       <c r="Q7" t="n">
-        <v>507</v>
+        <v>85</v>
       </c>
       <c r="R7" t="n">
-        <v>2654</v>
+        <v>480</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1126,17 +1126,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1102972683</t>
+          <t>1318401535</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1102972683</t>
+          <t>https://m.place.naver.com/place/1318401535</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1148,29 +1148,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>아틀라스&amp;바른자세 운동센터</t>
+          <t>팀아지트체형교정pt</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>atlascs@naver.com</t>
+          <t>hyunjsh1@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1341-0145</t>
+          <t>0507-1410-8050</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>제주 제주시 과천로 31 4층</t>
+          <t>제주 제주시 노형9길 9-3 1층 팀아지트</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/jejuatlas/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1180,7 +1180,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wcfqcj</t>
+          <t>https://talk.naver.com/ct/wc9trv</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1209,13 +1209,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>129</v>
+        <v>86</v>
       </c>
       <c r="Q8" t="n">
-        <v>188</v>
+        <v>160</v>
       </c>
       <c r="R8" t="n">
-        <v>317</v>
+        <v>246</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1224,51 +1224,51 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>37264400</t>
+          <t>35136135</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37264400</t>
+          <t>https://m.place.naver.com/place/35136135</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>팀아지트체형교정pt</t>
+          <t>마인드휘트니스 노형점 헬스&amp;PT&amp;필라테스</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>hyunjsh1@naver.com</t>
+          <t>mindfitness15@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1410-8050</t>
+          <t>0507-1439-0799</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>제주 제주시 노형9길 9-3 1층 팀아지트</t>
+          <t>제주 제주시 월랑로 1 8층, 9층 마인드휘트니스 노형점</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/hyunjsh1</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1278,12 +1278,12 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wc9trv</t>
+          <t>https://talk.naver.com/ct/w4g2g5</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1307,13 +1307,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>86</v>
+        <v>819</v>
       </c>
       <c r="Q9" t="n">
-        <v>160</v>
+        <v>780</v>
       </c>
       <c r="R9" t="n">
-        <v>246</v>
+        <v>1599</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1322,17 +1322,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>35136135</t>
+          <t>1485921447</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/35136135</t>
+          <t>https://m.place.naver.com/place/1485921447</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1344,29 +1344,25 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>마인드휘트니스 PT&amp;필라테스&amp;요가 동홍점</t>
+          <t>유제이 PT&amp;필라테스 노형점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>mindfitness7@naver.com</t>
+          <t>ekfkdgo4330@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0507-1352-0797</t>
-        </is>
-      </c>
+      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>제주 서귀포시 동홍중앙로 55 2층,3층</t>
+          <t>제주 제주시 남녕로 25 리안스테이노형 3층 302호</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/mindfitness7</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1376,12 +1372,12 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1391,7 +1387,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4yf5p</t>
+          <t>https://talk.naver.com/ct/wn4n9ww</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1405,13 +1401,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>741</v>
+        <v>176</v>
       </c>
       <c r="Q10" t="n">
-        <v>768</v>
+        <v>140</v>
       </c>
       <c r="R10" t="n">
-        <v>1509</v>
+        <v>316</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1420,17 +1416,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1069617460</t>
+          <t>1722027239</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1069617460</t>
+          <t>https://m.place.naver.com/place/1722027239</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1442,29 +1438,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>마인드휘트니스 노형점 헬스&amp;PT&amp;필라테스</t>
+          <t>리셋 중문점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>mindfitness15@naver.com</t>
+          <t>reset_jungmun@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1439-0799</t>
+          <t>0507-1393-1529</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>제주 제주시 월랑로 1 8층, 9층 마인드휘트니스 노형점</t>
+          <t>제주 서귀포시 대포중앙로 6-8 3층 리셋 중문점</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/mindfitness15</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1474,12 +1470,12 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1489,7 +1485,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4g2g5</t>
+          <t>https://talk.naver.com/ct/wliznta</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1503,13 +1499,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>819</v>
+        <v>5</v>
       </c>
       <c r="Q11" t="n">
-        <v>780</v>
+        <v>20</v>
       </c>
       <c r="R11" t="n">
-        <v>1599</v>
+        <v>25</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1518,17 +1514,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1485921447</t>
+          <t>2058980846</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1485921447</t>
+          <t>https://m.place.naver.com/place/2058980846</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/제주_PT.xlsx
+++ b/naver-place-crawler/results_health/제주_PT.xlsx
@@ -680,7 +680,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/mindfitness23</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -690,12 +690,12 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -778,7 +778,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/custom_hallim/</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -876,7 +876,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/mindfitness13</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -886,12 +886,12 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/jejuatlas/</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1072,7 +1072,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/bareum_fitness</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1082,12 +1082,12 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1170,7 +1170,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/hyunjsh1</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1180,12 +1180,12 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/mindfitness15</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1278,12 +1278,12 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1344,25 +1344,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>유제이 PT&amp;필라테스 노형점</t>
+          <t>마인드휘트니스 PT&amp;필라테스&amp;요가 동홍점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ekfkdgo4330@naver.com</t>
+          <t>mindfitness7@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0507-1352-0797</t>
+        </is>
+      </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>제주 제주시 남녕로 25 리안스테이노형 3층 302호</t>
+          <t>제주 서귀포시 동홍중앙로 55 2층,3층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/mindfitness7</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1372,12 +1376,12 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1387,7 +1391,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wn4n9ww</t>
+          <t>https://talk.naver.com/ct/w4yf5p</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1401,13 +1405,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>176</v>
+        <v>741</v>
       </c>
       <c r="Q10" t="n">
-        <v>140</v>
+        <v>768</v>
       </c>
       <c r="R10" t="n">
-        <v>316</v>
+        <v>1509</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1416,12 +1420,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1722027239</t>
+          <t>1069617460</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1722027239</t>
+          <t>https://m.place.naver.com/place/1069617460</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1438,34 +1442,34 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>리셋 중문점</t>
+          <t>마인드휘트니스 PT&amp;필라테스&amp;요가 서홍점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>reset_jungmun@naver.com</t>
+          <t>mindfitness2@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1393-1529</t>
+          <t>0507-1446-0790</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>제주 서귀포시 대포중앙로 6-8 3층 리셋 중문점</t>
+          <t>제주 서귀포시 홍중로 99 2, 3, 4층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.mindfitness-official.com/</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1475,7 +1479,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1485,12 +1489,12 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wliznta</t>
+          <t>https://talk.naver.com/ct/w47xu3</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1499,13 +1503,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>5</v>
+        <v>1016</v>
       </c>
       <c r="Q11" t="n">
-        <v>20</v>
+        <v>444</v>
       </c>
       <c r="R11" t="n">
-        <v>25</v>
+        <v>1460</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1514,12 +1518,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2058980846</t>
+          <t>1647569204</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2058980846</t>
+          <t>https://m.place.naver.com/place/1647569204</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">

--- a/naver-place-crawler/results_health/제주_PT.xlsx
+++ b/naver-place-crawler/results_health/제주_PT.xlsx
@@ -426,7 +426,7 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="33" customWidth="1" min="7" max="7"/>
+    <col width="50" customWidth="1" min="7" max="7"/>
     <col width="42" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
@@ -1148,29 +1148,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>팀아지트체형교정pt</t>
+          <t>무브멘탈랩 &amp; 뉴로필라테스</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>hyunjsh1@naver.com</t>
+          <t>move_9@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1410-8050</t>
+          <t>0507-1341-2075</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>제주 제주시 노형9길 9-3 1층 팀아지트</t>
+          <t>제주 서귀포시 성산읍 일주동로4120번길 23-20 신관 2층, 무브멘탈랩 트레이닝센터</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/hyunjsh1</t>
+          <t>https://linktr.ee/jeju_neuro</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1190,14 +1190,10 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wc9trv</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
           <t>X</t>
@@ -1209,13 +1205,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="Q8" t="n">
-        <v>160</v>
+        <v>93</v>
       </c>
       <c r="R8" t="n">
-        <v>246</v>
+        <v>178</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1224,12 +1220,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>35136135</t>
+          <t>1037944274</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/35136135</t>
+          <t>https://m.place.naver.com/place/1037944274</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">

--- a/naver-place-crawler/results_health/제주_PT.xlsx
+++ b/naver-place-crawler/results_health/제주_PT.xlsx
@@ -1242,29 +1242,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>마인드휘트니스 노형점 헬스&amp;PT&amp;필라테스</t>
+          <t>마인드휘트니스 PT&amp;필라테스&amp;요가 동홍점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>mindfitness15@naver.com</t>
+          <t>mindfitness7@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1439-0799</t>
+          <t>0507-1352-0797</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>제주 제주시 월랑로 1 8층, 9층 마인드휘트니스 노형점</t>
+          <t>제주 서귀포시 동홍중앙로 55 2층,3층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/mindfitness15</t>
+          <t>https://blog.naver.com/mindfitness7</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1289,7 +1289,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4g2g5</t>
+          <t>https://talk.naver.com/ct/w4yf5p</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1303,13 +1303,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>819</v>
+        <v>741</v>
       </c>
       <c r="Q9" t="n">
-        <v>780</v>
+        <v>768</v>
       </c>
       <c r="R9" t="n">
-        <v>1599</v>
+        <v>1509</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1485921447</t>
+          <t>1069617460</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1485921447</t>
+          <t>https://m.place.naver.com/place/1069617460</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1340,39 +1340,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>마인드휘트니스 PT&amp;필라테스&amp;요가 동홍점</t>
+          <t>마인드휘트니스 PT&amp;필라테스&amp;요가 서홍점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>mindfitness7@naver.com</t>
+          <t>mindfitness2@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1352-0797</t>
+          <t>0507-1446-0790</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>제주 서귀포시 동홍중앙로 55 2층,3층</t>
+          <t>제주 서귀포시 홍중로 99 2, 3, 4층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/mindfitness7</t>
+          <t>https://www.mindfitness-official.com/</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4yf5p</t>
+          <t>https://talk.naver.com/ct/w47xu3</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1401,13 +1401,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>741</v>
+        <v>1016</v>
       </c>
       <c r="Q10" t="n">
-        <v>768</v>
+        <v>444</v>
       </c>
       <c r="R10" t="n">
-        <v>1509</v>
+        <v>1460</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1069617460</t>
+          <t>1647569204</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1069617460</t>
+          <t>https://m.place.naver.com/place/1647569204</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1438,44 +1438,40 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>마인드휘트니스 PT&amp;필라테스&amp;요가 서홍점</t>
+          <t>유제이 PT&amp;필라테스 노형점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>mindfitness2@naver.com</t>
+          <t>ohssang988@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>0507-1446-0790</t>
-        </is>
-      </c>
+      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>제주 서귀포시 홍중로 99 2, 3, 4층</t>
+          <t>제주 제주시 남녕로 25 리안스테이노형 3층 302호</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.mindfitness-official.com/</t>
+          <t>https://www.instagram.com/uj_pt0125</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1485,12 +1481,12 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w47xu3</t>
+          <t>https://talk.naver.com/ct/wn4n9ww</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1499,13 +1495,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>1016</v>
+        <v>176</v>
       </c>
       <c r="Q11" t="n">
-        <v>444</v>
+        <v>140</v>
       </c>
       <c r="R11" t="n">
-        <v>1460</v>
+        <v>316</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1514,12 +1510,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1647569204</t>
+          <t>1722027239</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1647569204</t>
+          <t>https://m.place.naver.com/place/1722027239</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">

--- a/naver-place-crawler/results_health/제주_PT.xlsx
+++ b/naver-place-crawler/results_health/제주_PT.xlsx
@@ -646,7 +646,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -744,7 +744,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -842,7 +842,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -940,7 +940,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1230,7 +1230,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1242,29 +1242,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>마인드휘트니스 PT&amp;필라테스&amp;요가 동홍점</t>
+          <t>마인드휘트니스 노형점 헬스&amp;PT&amp;필라테스</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>mindfitness7@naver.com</t>
+          <t>mindfitness15@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1352-0797</t>
+          <t>0507-1439-0799</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>제주 서귀포시 동홍중앙로 55 2층,3층</t>
+          <t>제주 제주시 월랑로 1 8층, 9층 마인드휘트니스 노형점</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/mindfitness7</t>
+          <t>https://blog.naver.com/mindfitness15</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1289,7 +1289,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4yf5p</t>
+          <t>https://talk.naver.com/ct/w4g2g5</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1303,13 +1303,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>741</v>
+        <v>819</v>
       </c>
       <c r="Q9" t="n">
-        <v>768</v>
+        <v>780</v>
       </c>
       <c r="R9" t="n">
-        <v>1509</v>
+        <v>1599</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1318,17 +1318,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1069617460</t>
+          <t>1485921447</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1069617460</t>
+          <t>https://m.place.naver.com/place/1485921447</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1340,44 +1340,40 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>마인드휘트니스 PT&amp;필라테스&amp;요가 서홍점</t>
+          <t>유제이 PT&amp;필라테스 노형점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>mindfitness2@naver.com</t>
+          <t>ohssang988@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0507-1446-0790</t>
-        </is>
-      </c>
+      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>제주 서귀포시 홍중로 99 2, 3, 4층</t>
+          <t>제주 제주시 남녕로 25 리안스테이노형 3층 302호</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.mindfitness-official.com/</t>
+          <t>https://www.instagram.com/uj_pt0125</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1387,12 +1383,12 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w47xu3</t>
+          <t>https://talk.naver.com/ct/wn4n9ww</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1401,13 +1397,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1016</v>
+        <v>176</v>
       </c>
       <c r="Q10" t="n">
-        <v>444</v>
+        <v>140</v>
       </c>
       <c r="R10" t="n">
-        <v>1460</v>
+        <v>316</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1416,17 +1412,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1647569204</t>
+          <t>1722027239</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1647569204</t>
+          <t>https://m.place.naver.com/place/1722027239</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1438,25 +1434,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>유제이 PT&amp;필라테스 노형점</t>
+          <t>리셋 중문점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ohssang988@naver.com</t>
+          <t>reset_jungmun@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0507-1393-1529</t>
+        </is>
+      </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>제주 제주시 남녕로 25 리안스테이노형 3층 302호</t>
+          <t>제주 서귀포시 대포중앙로 6-8 3층 리셋 중문점</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/uj_pt0125</t>
+          <t>https://blog.naver.com/reset_jungmun</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wn4n9ww</t>
+          <t>https://talk.naver.com/ct/wliznta</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1495,13 +1495,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>176</v>
+        <v>5</v>
       </c>
       <c r="Q11" t="n">
-        <v>140</v>
+        <v>20</v>
       </c>
       <c r="R11" t="n">
-        <v>316</v>
+        <v>25</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1510,17 +1510,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1722027239</t>
+          <t>2058980846</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1722027239</t>
+          <t>https://m.place.naver.com/place/2058980846</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/제주_PT.xlsx
+++ b/naver-place-crawler/results_health/제주_PT.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:V10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -624,10 +624,10 @@
         <v>126</v>
       </c>
       <c r="Q2" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="R2" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -1045,39 +1045,39 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>바름휘트니스 노형점</t>
+          <t>코어스포츠제주 헬스&amp;PT</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>bareum_fitness@naver.com</t>
+          <t>core_sport_jeju@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1302-4841</t>
+          <t>0507-1409-1645</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>제주 제주시 원노형로 54 3층</t>
+          <t>제주 제주시 도령로 64 3층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/bareum_fitness</t>
+          <t>http://coresportsjeju.com/</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1097,7 +1097,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wfn65t0</t>
+          <t>https://talk.naver.com/ct/wrehaip</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1111,13 +1111,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>395</v>
+        <v>157</v>
       </c>
       <c r="Q7" t="n">
-        <v>85</v>
+        <v>567</v>
       </c>
       <c r="R7" t="n">
-        <v>480</v>
+        <v>724</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1126,12 +1126,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1318401535</t>
+          <t>1159226809</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1318401535</t>
+          <t>https://m.place.naver.com/place/1159226809</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1242,29 +1242,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>마인드휘트니스 노형점 헬스&amp;PT&amp;필라테스</t>
+          <t>마인드휘트니스 PT&amp;필라테스&amp;요가 동홍점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>mindfitness15@naver.com</t>
+          <t>mindfitness7@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1439-0799</t>
+          <t>0507-1352-0797</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>제주 제주시 월랑로 1 8층, 9층 마인드휘트니스 노형점</t>
+          <t>제주 서귀포시 동홍중앙로 55 2층,3층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/mindfitness15</t>
+          <t>https://blog.naver.com/mindfitness7</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1289,7 +1289,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4g2g5</t>
+          <t>https://talk.naver.com/ct/w4yf5p</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1303,13 +1303,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>819</v>
+        <v>741</v>
       </c>
       <c r="Q9" t="n">
-        <v>780</v>
+        <v>768</v>
       </c>
       <c r="R9" t="n">
-        <v>1599</v>
+        <v>1509</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1485921447</t>
+          <t>1069617460</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1485921447</t>
+          <t>https://m.place.naver.com/place/1069617460</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1340,40 +1340,44 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>유제이 PT&amp;필라테스 노형점</t>
+          <t>마인드휘트니스 PT&amp;필라테스&amp;요가 서홍점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ohssang988@naver.com</t>
+          <t>mindfitness2@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0507-1446-0790</t>
+        </is>
+      </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>제주 제주시 남녕로 25 리안스테이노형 3층 302호</t>
+          <t>제주 서귀포시 홍중로 99 2, 3, 4층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/uj_pt0125</t>
+          <t>https://www.mindfitness-official.com/</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1383,12 +1387,12 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wn4n9ww</t>
+          <t>https://talk.naver.com/ct/w47xu3</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1397,13 +1401,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>176</v>
+        <v>1016</v>
       </c>
       <c r="Q10" t="n">
-        <v>140</v>
+        <v>444</v>
       </c>
       <c r="R10" t="n">
-        <v>316</v>
+        <v>1460</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1412,113 +1416,15 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1722027239</t>
+          <t>1647569204</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1722027239</t>
+          <t>https://m.place.naver.com/place/1647569204</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>헬스장</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>리셋 중문점</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>reset_jungmun@naver.com</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>0507-1393-1529</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>제주 서귀포시 대포중앙로 6-8 3층 리셋 중문점</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/reset_jungmun</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wliznta</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P11" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>20</v>
-      </c>
-      <c r="R11" t="n">
-        <v>25</v>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>2058980846</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/2058980846</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>

--- a/naver-place-crawler/results_health/제주_PT.xlsx
+++ b/naver-place-crawler/results_health/제주_PT.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V10"/>
+  <dimension ref="A1:V11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -658,29 +658,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>마인드휘트니스 중앙점</t>
+          <t>사람휘트니스 이도7호점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>mindfitness23@naver.com</t>
+          <t>saram_ido@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1468-2371</t>
+          <t>0507-1404-1264</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>제주 제주시 중앙로 53 JJ아트뷰타워 3, 4층</t>
+          <t>제주 제주시 연삼로 424</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/mindfitness23</t>
+          <t>https://blog.naver.com/saram_ido</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -705,7 +705,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wo03pkw</t>
+          <t>https://talk.naver.com/ct/w5yc0j</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1536</v>
+        <v>273</v>
       </c>
       <c r="Q3" t="n">
-        <v>541</v>
+        <v>461</v>
       </c>
       <c r="R3" t="n">
-        <v>2077</v>
+        <v>734</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -734,12 +734,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1840405943</t>
+          <t>1089331988</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1840405943</t>
+          <t>https://m.place.naver.com/place/1089331988</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -751,34 +751,34 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>커스텀짐 한림점</t>
+          <t>마인드휘트니스 중앙점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>customhallim@naver.com</t>
+          <t>mindfitness23@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1363-2448</t>
+          <t>0507-1468-2371</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>제주 제주시 한림읍 한림중앙로 61-14</t>
+          <t>제주 제주시 중앙로 53 JJ아트뷰타워 3, 4층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/custom_hallim/</t>
+          <t>https://blog.naver.com/mindfitness23</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -803,7 +803,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w40eab</t>
+          <t>https://talk.naver.com/ct/wo03pkw</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>752</v>
+        <v>1538</v>
       </c>
       <c r="Q4" t="n">
-        <v>169</v>
+        <v>541</v>
       </c>
       <c r="R4" t="n">
-        <v>921</v>
+        <v>2079</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -832,12 +832,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1674334378</t>
+          <t>1840405943</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1674334378</t>
+          <t>https://m.place.naver.com/place/1840405943</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -849,39 +849,39 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>마인드휘트니스 제주공항점</t>
+          <t>커스텀짐 한림점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>mindfitness13@naver.com</t>
+          <t>customhallim@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1348-0798</t>
+          <t>0507-1363-2448</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>제주 제주시 도령로 167 에이동 2층, 3층</t>
+          <t>제주 제주시 한림읍 한림중앙로 61-14</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/mindfitness13</t>
+          <t>https://www.instagram.com/custom_hallim/</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4ptgx</t>
+          <t>https://talk.naver.com/ct/w40eab</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -915,13 +915,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>2149</v>
+        <v>752</v>
       </c>
       <c r="Q5" t="n">
-        <v>507</v>
+        <v>169</v>
       </c>
       <c r="R5" t="n">
-        <v>2656</v>
+        <v>921</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -930,12 +930,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1102972683</t>
+          <t>1674334378</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1102972683</t>
+          <t>https://m.place.naver.com/place/1674334378</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -947,34 +947,34 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>아틀라스&amp;바른자세 운동센터</t>
+          <t>마인드휘트니스 제주공항점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>atlascs@naver.com</t>
+          <t>mindfitness13@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1341-0145</t>
+          <t>0507-1348-0798</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>제주 제주시 과천로 31 4층</t>
+          <t>제주 제주시 도령로 167 에이동 2층, 3층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/jejuatlas/</t>
+          <t>https://blog.naver.com/mindfitness13</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -989,7 +989,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -999,7 +999,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wcfqcj</t>
+          <t>https://talk.naver.com/ct/w4ptgx</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1013,13 +1013,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>129</v>
+        <v>2150</v>
       </c>
       <c r="Q6" t="n">
-        <v>188</v>
+        <v>507</v>
       </c>
       <c r="R6" t="n">
-        <v>317</v>
+        <v>2657</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1028,12 +1028,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>37264400</t>
+          <t>1102972683</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37264400</t>
+          <t>https://m.place.naver.com/place/1102972683</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1050,34 +1050,34 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>코어스포츠제주 헬스&amp;PT</t>
+          <t>아틀라스&amp;바른자세 운동센터</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>core_sport_jeju@naver.com</t>
+          <t>atlascs@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1409-1645</t>
+          <t>0507-1341-0145</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>제주 제주시 도령로 64 3층</t>
+          <t>제주 제주시 과천로 31 4층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>http://coresportsjeju.com/</t>
+          <t>https://www.instagram.com/jejuatlas/</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1087,7 +1087,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1097,7 +1097,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wrehaip</t>
+          <t>https://talk.naver.com/ct/wcfqcj</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1111,13 +1111,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>157</v>
+        <v>129</v>
       </c>
       <c r="Q7" t="n">
-        <v>567</v>
+        <v>188</v>
       </c>
       <c r="R7" t="n">
-        <v>724</v>
+        <v>317</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1126,12 +1126,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1159226809</t>
+          <t>37264400</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1159226809</t>
+          <t>https://m.place.naver.com/place/37264400</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1148,34 +1148,34 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>무브멘탈랩 &amp; 뉴로필라테스</t>
+          <t>코어스포츠제주 헬스&amp;PT</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>move_9@naver.com</t>
+          <t>core_sport_jeju@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1341-2075</t>
+          <t>0507-1409-1645</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>제주 서귀포시 성산읍 일주동로4120번길 23-20 신관 2층, 무브멘탈랩 트레이닝센터</t>
+          <t>제주 제주시 도령로 64 3층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://linktr.ee/jeju_neuro</t>
+          <t>http://coresportsjeju.com/</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1190,10 +1190,14 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wrehaip</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr">
         <is>
           <t>X</t>
@@ -1205,13 +1209,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>85</v>
+        <v>158</v>
       </c>
       <c r="Q8" t="n">
-        <v>93</v>
+        <v>567</v>
       </c>
       <c r="R8" t="n">
-        <v>178</v>
+        <v>725</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1220,12 +1224,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1037944274</t>
+          <t>1159226809</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1037944274</t>
+          <t>https://m.place.naver.com/place/1159226809</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1237,34 +1241,34 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>마인드휘트니스 PT&amp;필라테스&amp;요가 동홍점</t>
+          <t>무브멘탈랩 &amp; 뉴로필라테스</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>mindfitness7@naver.com</t>
+          <t>move_9@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1352-0797</t>
+          <t>0507-1341-2075</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>제주 서귀포시 동홍중앙로 55 2층,3층</t>
+          <t>제주 서귀포시 성산읍 일주동로4120번길 23-20 신관 2층, 무브멘탈랩 트레이닝센터</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/mindfitness7</t>
+          <t>https://linktr.ee/jeju_neuro</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1284,14 +1288,10 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4yf5p</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
           <t>X</t>
@@ -1303,13 +1303,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>741</v>
+        <v>85</v>
       </c>
       <c r="Q9" t="n">
-        <v>768</v>
+        <v>94</v>
       </c>
       <c r="R9" t="n">
-        <v>1509</v>
+        <v>179</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1069617460</t>
+          <t>1037944274</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1069617460</t>
+          <t>https://m.place.naver.com/place/1037944274</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1340,39 +1340,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>마인드휘트니스 PT&amp;필라테스&amp;요가 서홍점</t>
+          <t>마인드휘트니스 노형점 헬스&amp;PT&amp;필라테스</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>mindfitness2@naver.com</t>
+          <t>mindfitness15@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1446-0790</t>
+          <t>0507-1439-0799</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>제주 서귀포시 홍중로 99 2, 3, 4층</t>
+          <t>제주 제주시 월랑로 1 8층, 9층 마인드휘트니스 노형점</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.mindfitness-official.com/</t>
+          <t>https://blog.naver.com/mindfitness15</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w47xu3</t>
+          <t>https://talk.naver.com/ct/w4g2g5</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1401,13 +1401,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1016</v>
+        <v>819</v>
       </c>
       <c r="Q10" t="n">
-        <v>444</v>
+        <v>781</v>
       </c>
       <c r="R10" t="n">
-        <v>1460</v>
+        <v>1600</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1416,15 +1416,113 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1647569204</t>
+          <t>1485921447</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1647569204</t>
+          <t>https://m.place.naver.com/place/1485921447</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>마인드휘트니스 PT&amp;필라테스&amp;요가 동홍점</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>mindfitness7@naver.com</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0507-1352-0797</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>제주 서귀포시 동홍중앙로 55 2층,3층</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/mindfitness7</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4yf5p</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>741</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>768</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1509</v>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>1069617460</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1069617460</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>

--- a/naver-place-crawler/results_health/제주_PT.xlsx
+++ b/naver-place-crawler/results_health/제주_PT.xlsx
@@ -646,7 +646,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -658,29 +658,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>사람휘트니스 이도7호점</t>
+          <t>마인드휘트니스 중앙점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>saram_ido@naver.com</t>
+          <t>mindfitness23@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1404-1264</t>
+          <t>0507-1468-2371</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>제주 제주시 연삼로 424</t>
+          <t>제주 제주시 중앙로 53 JJ아트뷰타워 3, 4층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/saram_ido</t>
+          <t>https://blog.naver.com/mindfitness23</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -705,7 +705,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5yc0j</t>
+          <t>https://talk.naver.com/ct/wo03pkw</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>273</v>
+        <v>1538</v>
       </c>
       <c r="Q3" t="n">
-        <v>461</v>
+        <v>541</v>
       </c>
       <c r="R3" t="n">
-        <v>734</v>
+        <v>2079</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -734,51 +734,51 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1089331988</t>
+          <t>1840405943</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1089331988</t>
+          <t>https://m.place.naver.com/place/1840405943</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>마인드휘트니스 중앙점</t>
+          <t>커스텀짐 한림점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>mindfitness23@naver.com</t>
+          <t>customhallim@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1468-2371</t>
+          <t>0507-1363-2448</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>제주 제주시 중앙로 53 JJ아트뷰타워 3, 4층</t>
+          <t>제주 제주시 한림읍 한림중앙로 61-14</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/mindfitness23</t>
+          <t>https://www.instagram.com/custom_hallim/</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -803,7 +803,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wo03pkw</t>
+          <t>https://talk.naver.com/ct/w40eab</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1538</v>
+        <v>752</v>
       </c>
       <c r="Q4" t="n">
-        <v>541</v>
+        <v>169</v>
       </c>
       <c r="R4" t="n">
-        <v>2079</v>
+        <v>921</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -832,56 +832,56 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1840405943</t>
+          <t>1674334378</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1840405943</t>
+          <t>https://m.place.naver.com/place/1674334378</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>커스텀짐 한림점</t>
+          <t>마인드휘트니스 제주공항점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>customhallim@naver.com</t>
+          <t>mindfitness13@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1363-2448</t>
+          <t>0507-1348-0798</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>제주 제주시 한림읍 한림중앙로 61-14</t>
+          <t>제주 제주시 도령로 167 에이동 2층, 3층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/custom_hallim/</t>
+          <t>https://blog.naver.com/mindfitness13</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w40eab</t>
+          <t>https://talk.naver.com/ct/w4ptgx</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -915,13 +915,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>752</v>
+        <v>2151</v>
       </c>
       <c r="Q5" t="n">
-        <v>169</v>
+        <v>507</v>
       </c>
       <c r="R5" t="n">
-        <v>921</v>
+        <v>2658</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -930,51 +930,51 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1674334378</t>
+          <t>1102972683</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1674334378</t>
+          <t>https://m.place.naver.com/place/1102972683</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>마인드휘트니스 제주공항점</t>
+          <t>아틀라스&amp;바른자세 운동센터</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>mindfitness13@naver.com</t>
+          <t>atlascs@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1348-0798</t>
+          <t>0507-1341-0145</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>제주 제주시 도령로 167 에이동 2층, 3층</t>
+          <t>제주 제주시 과천로 31 4층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/mindfitness13</t>
+          <t>https://www.instagram.com/jejuatlas/</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -989,7 +989,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -999,7 +999,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4ptgx</t>
+          <t>https://talk.naver.com/ct/wcfqcj</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1013,13 +1013,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>2150</v>
+        <v>129</v>
       </c>
       <c r="Q6" t="n">
-        <v>507</v>
+        <v>188</v>
       </c>
       <c r="R6" t="n">
-        <v>2657</v>
+        <v>317</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1028,17 +1028,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1102972683</t>
+          <t>37264400</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1102972683</t>
+          <t>https://m.place.naver.com/place/37264400</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1050,34 +1050,34 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>아틀라스&amp;바른자세 운동센터</t>
+          <t>코어스포츠제주 헬스&amp;PT</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>atlascs@naver.com</t>
+          <t>core_sport_jeju@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1341-0145</t>
+          <t>0507-1409-1645</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>제주 제주시 과천로 31 4층</t>
+          <t>제주 제주시 도령로 64 3층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/jejuatlas/</t>
+          <t>http://coresportsjeju.com/</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1087,7 +1087,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1097,7 +1097,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wcfqcj</t>
+          <t>https://talk.naver.com/ct/wrehaip</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1111,13 +1111,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>129</v>
+        <v>158</v>
       </c>
       <c r="Q7" t="n">
-        <v>188</v>
+        <v>567</v>
       </c>
       <c r="R7" t="n">
-        <v>317</v>
+        <v>725</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1126,17 +1126,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>37264400</t>
+          <t>1159226809</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37264400</t>
+          <t>https://m.place.naver.com/place/1159226809</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1148,34 +1148,34 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>코어스포츠제주 헬스&amp;PT</t>
+          <t>무브멘탈랩 &amp; 뉴로필라테스</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>core_sport_jeju@naver.com</t>
+          <t>move_9@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1409-1645</t>
+          <t>0507-1341-2075</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>제주 제주시 도령로 64 3층</t>
+          <t>제주 서귀포시 성산읍 일주동로4120번길 23-20 신관 2층, 무브멘탈랩 트레이닝센터</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>http://coresportsjeju.com/</t>
+          <t>https://linktr.ee/jeju_neuro</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1190,14 +1190,10 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wrehaip</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
           <t>X</t>
@@ -1209,13 +1205,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>158</v>
+        <v>85</v>
       </c>
       <c r="Q8" t="n">
-        <v>567</v>
+        <v>94</v>
       </c>
       <c r="R8" t="n">
-        <v>725</v>
+        <v>179</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1224,51 +1220,51 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1159226809</t>
+          <t>1037944274</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1159226809</t>
+          <t>https://m.place.naver.com/place/1037944274</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>무브멘탈랩 &amp; 뉴로필라테스</t>
+          <t>마인드휘트니스 노형점 헬스&amp;PT&amp;필라테스</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>move_9@naver.com</t>
+          <t>mindfitness15@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1341-2075</t>
+          <t>0507-1439-0799</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>제주 서귀포시 성산읍 일주동로4120번길 23-20 신관 2층, 무브멘탈랩 트레이닝센터</t>
+          <t>제주 제주시 월랑로 1 8층, 9층 마인드휘트니스 노형점</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://linktr.ee/jeju_neuro</t>
+          <t>https://blog.naver.com/mindfitness15</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1288,10 +1284,14 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4g2g5</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr">
         <is>
           <t>X</t>
@@ -1303,13 +1303,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>85</v>
+        <v>819</v>
       </c>
       <c r="Q9" t="n">
-        <v>94</v>
+        <v>781</v>
       </c>
       <c r="R9" t="n">
-        <v>179</v>
+        <v>1600</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1318,17 +1318,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1037944274</t>
+          <t>1485921447</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1037944274</t>
+          <t>https://m.place.naver.com/place/1485921447</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1340,29 +1340,25 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>마인드휘트니스 노형점 헬스&amp;PT&amp;필라테스</t>
+          <t>유제이 PT&amp;필라테스 노형점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>mindfitness15@naver.com</t>
+          <t>ohssang988@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0507-1439-0799</t>
-        </is>
-      </c>
+      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>제주 제주시 월랑로 1 8층, 9층 마인드휘트니스 노형점</t>
+          <t>제주 제주시 남녕로 25 리안스테이노형 3층 302호</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/mindfitness15</t>
+          <t>https://www.instagram.com/uj_pt0125</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1377,7 +1373,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1387,7 +1383,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4g2g5</t>
+          <t>https://talk.naver.com/ct/wn4n9ww</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1401,13 +1397,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>819</v>
+        <v>176</v>
       </c>
       <c r="Q10" t="n">
-        <v>781</v>
+        <v>140</v>
       </c>
       <c r="R10" t="n">
-        <v>1600</v>
+        <v>316</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1416,17 +1412,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1485921447</t>
+          <t>1722027239</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1485921447</t>
+          <t>https://m.place.naver.com/place/1722027239</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1438,29 +1434,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>마인드휘트니스 PT&amp;필라테스&amp;요가 동홍점</t>
+          <t>리셋 중문점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>mindfitness7@naver.com</t>
+          <t>reset_jungmun@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1352-0797</t>
+          <t>0507-1393-1529</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>제주 서귀포시 동홍중앙로 55 2층,3층</t>
+          <t>제주 서귀포시 대포중앙로 6-8 3층 리셋 중문점</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/mindfitness7</t>
+          <t>https://blog.naver.com/reset_jungmun</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1485,7 +1481,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4yf5p</t>
+          <t>https://talk.naver.com/ct/wliznta</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1499,13 +1495,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>741</v>
+        <v>5</v>
       </c>
       <c r="Q11" t="n">
-        <v>768</v>
+        <v>20</v>
       </c>
       <c r="R11" t="n">
-        <v>1509</v>
+        <v>25</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1514,17 +1510,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1069617460</t>
+          <t>2058980846</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1069617460</t>
+          <t>https://m.place.naver.com/place/2058980846</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/제주_PT.xlsx
+++ b/naver-place-crawler/results_health/제주_PT.xlsx
@@ -417,12 +417,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:V10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="29" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
@@ -564,29 +564,29 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>정글짐 구남점</t>
+          <t>사람휘트니스 이도7호점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>junglegyminherfit@naver.com</t>
+          <t>saram_ido@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1380-2950</t>
+          <t>0507-1404-1264</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>제주 제주시 구남동8길 58 올레마트 2층 정글짐</t>
+          <t>제주 제주시 연삼로 424</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/junglegyminherfit</t>
+          <t>https://blog.naver.com/saram_ido</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -606,10 +606,14 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5yc0j</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr">
         <is>
           <t>X</t>
@@ -617,17 +621,17 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>126</v>
+        <v>273</v>
       </c>
       <c r="Q2" t="n">
-        <v>84</v>
+        <v>461</v>
       </c>
       <c r="R2" t="n">
-        <v>210</v>
+        <v>734</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,12 +640,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1471742099</t>
+          <t>1089331988</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1471742099</t>
+          <t>https://m.place.naver.com/place/1089331988</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -653,34 +657,34 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>마인드휘트니스 중앙점</t>
+          <t>커스텀짐 한림점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>mindfitness23@naver.com</t>
+          <t>customhallim@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1468-2371</t>
+          <t>0507-1363-2448</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>제주 제주시 중앙로 53 JJ아트뷰타워 3, 4층</t>
+          <t>제주 제주시 한림읍 한림중앙로 61-14</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/mindfitness23</t>
+          <t>https://www.instagram.com/custom_hallim/</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -695,7 +699,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -705,7 +709,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wo03pkw</t>
+          <t>https://talk.naver.com/ct/w40eab</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -719,13 +723,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1538</v>
+        <v>753</v>
       </c>
       <c r="Q3" t="n">
-        <v>541</v>
+        <v>169</v>
       </c>
       <c r="R3" t="n">
-        <v>2079</v>
+        <v>922</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -734,12 +738,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1840405943</t>
+          <t>1674334378</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1840405943</t>
+          <t>https://m.place.naver.com/place/1674334378</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -751,34 +755,34 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>커스텀짐 한림점</t>
+          <t>마인드휘트니스 제주공항점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>customhallim@naver.com</t>
+          <t>mindfitness13@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1363-2448</t>
+          <t>0507-1348-0798</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>제주 제주시 한림읍 한림중앙로 61-14</t>
+          <t>제주 제주시 도령로 167 에이동 2층, 3층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/custom_hallim/</t>
+          <t>https://blog.naver.com/mindfitness13</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -793,7 +797,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -803,7 +807,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w40eab</t>
+          <t>https://talk.naver.com/ct/w4ptgx</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -817,13 +821,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>752</v>
+        <v>2153</v>
       </c>
       <c r="Q4" t="n">
-        <v>169</v>
+        <v>507</v>
       </c>
       <c r="R4" t="n">
-        <v>921</v>
+        <v>2660</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -832,12 +836,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1674334378</t>
+          <t>1102972683</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1674334378</t>
+          <t>https://m.place.naver.com/place/1102972683</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -849,34 +853,34 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>마인드휘트니스 제주공항점</t>
+          <t>아틀라스&amp;바른자세 운동센터</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>mindfitness13@naver.com</t>
+          <t>atlascs@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1348-0798</t>
+          <t>0507-1341-0145</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>제주 제주시 도령로 167 에이동 2층, 3층</t>
+          <t>제주 제주시 과천로 31 4층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/mindfitness13</t>
+          <t>https://www.instagram.com/jejuatlas/</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -891,7 +895,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -901,7 +905,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4ptgx</t>
+          <t>https://talk.naver.com/ct/wcfqcj</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -915,13 +919,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>2151</v>
+        <v>129</v>
       </c>
       <c r="Q5" t="n">
-        <v>507</v>
+        <v>188</v>
       </c>
       <c r="R5" t="n">
-        <v>2658</v>
+        <v>317</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -930,12 +934,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1102972683</t>
+          <t>37264400</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1102972683</t>
+          <t>https://m.place.naver.com/place/37264400</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -952,29 +956,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>아틀라스&amp;바른자세 운동센터</t>
+          <t>코어스포츠제주 헬스&amp;PT</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>atlascs@naver.com</t>
+          <t>core_sport_jeju@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1341-0145</t>
+          <t>0507-1409-1645</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>제주 제주시 과천로 31 4층</t>
+          <t>제주 제주시 도령로 64 3층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/jejuatlas/</t>
+          <t>http://coresportsjeju.com/</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -999,7 +1003,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wcfqcj</t>
+          <t>https://talk.naver.com/ct/wrehaip</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1013,13 +1017,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>129</v>
+        <v>158</v>
       </c>
       <c r="Q6" t="n">
-        <v>188</v>
+        <v>567</v>
       </c>
       <c r="R6" t="n">
-        <v>317</v>
+        <v>725</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1028,12 +1032,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>37264400</t>
+          <t>1159226809</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37264400</t>
+          <t>https://m.place.naver.com/place/1159226809</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1050,34 +1054,34 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>코어스포츠제주 헬스&amp;PT</t>
+          <t>무브멘탈랩 &amp; 뉴로필라테스</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>core_sport_jeju@naver.com</t>
+          <t>move_9@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1409-1645</t>
+          <t>0507-1341-2075</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>제주 제주시 도령로 64 3층</t>
+          <t>제주 서귀포시 성산읍 일주동로4120번길 23-20 신관 2층, 무브멘탈랩 트레이닝센터</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>http://coresportsjeju.com/</t>
+          <t>https://linktr.ee/jeju_neuro</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1092,14 +1096,10 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wrehaip</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1111,13 +1111,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>158</v>
+        <v>85</v>
       </c>
       <c r="Q7" t="n">
-        <v>567</v>
+        <v>94</v>
       </c>
       <c r="R7" t="n">
-        <v>725</v>
+        <v>179</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1126,12 +1126,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1159226809</t>
+          <t>1037944274</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1159226809</t>
+          <t>https://m.place.naver.com/place/1037944274</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1143,34 +1143,34 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>무브멘탈랩 &amp; 뉴로필라테스</t>
+          <t>마인드휘트니스 PT&amp;필라테스&amp;요가 동홍점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>move_9@naver.com</t>
+          <t>mindfitness7@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1341-2075</t>
+          <t>0507-1352-0797</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>제주 서귀포시 성산읍 일주동로4120번길 23-20 신관 2층, 무브멘탈랩 트레이닝센터</t>
+          <t>제주 서귀포시 동홍중앙로 55 2층,3층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://linktr.ee/jeju_neuro</t>
+          <t>https://blog.naver.com/mindfitness7</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1190,10 +1190,14 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4yf5p</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr">
         <is>
           <t>X</t>
@@ -1205,13 +1209,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>85</v>
+        <v>741</v>
       </c>
       <c r="Q8" t="n">
-        <v>94</v>
+        <v>768</v>
       </c>
       <c r="R8" t="n">
-        <v>179</v>
+        <v>1509</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1220,12 +1224,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1037944274</t>
+          <t>1069617460</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1037944274</t>
+          <t>https://m.place.naver.com/place/1069617460</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1242,29 +1246,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>마인드휘트니스 노형점 헬스&amp;PT&amp;필라테스</t>
+          <t>마인드휘트니스 PT&amp;필라테스&amp;요가 서홍점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>mindfitness15@naver.com</t>
+          <t>mindfitness2@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1439-0799</t>
+          <t>0507-1446-0790</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>제주 제주시 월랑로 1 8층, 9층 마인드휘트니스 노형점</t>
+          <t>제주 서귀포시 홍중로 99 2, 3, 4층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/mindfitness15</t>
+          <t>https://www.mindfitness-official.com/</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1279,7 +1283,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1289,7 +1293,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4g2g5</t>
+          <t>https://talk.naver.com/ct/w47xu3</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1303,13 +1307,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>819</v>
+        <v>1016</v>
       </c>
       <c r="Q9" t="n">
-        <v>781</v>
+        <v>445</v>
       </c>
       <c r="R9" t="n">
-        <v>1600</v>
+        <v>1461</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1318,12 +1322,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1485921447</t>
+          <t>1647569204</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1485921447</t>
+          <t>https://m.place.naver.com/place/1647569204</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1340,25 +1344,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>유제이 PT&amp;필라테스 노형점</t>
+          <t>마인드휘트니스 중앙점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ohssang988@naver.com</t>
+          <t>mindfitness23@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0507-1468-2371</t>
+        </is>
+      </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>제주 제주시 남녕로 25 리안스테이노형 3층 302호</t>
+          <t>제주 제주시 중앙로 53 JJ아트뷰타워 3, 4층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/uj_pt0125</t>
+          <t>https://blog.naver.com/mindfitness23</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1373,7 +1381,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1383,7 +1391,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wn4n9ww</t>
+          <t>https://talk.naver.com/ct/wo03pkw</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1397,13 +1405,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>176</v>
+        <v>1538</v>
       </c>
       <c r="Q10" t="n">
-        <v>140</v>
+        <v>541</v>
       </c>
       <c r="R10" t="n">
-        <v>316</v>
+        <v>2079</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1412,113 +1420,15 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1722027239</t>
+          <t>1840405943</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1722027239</t>
+          <t>https://m.place.naver.com/place/1840405943</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>헬스장</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>리셋 중문점</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>reset_jungmun@naver.com</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>0507-1393-1529</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>제주 서귀포시 대포중앙로 6-8 3층 리셋 중문점</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/reset_jungmun</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wliznta</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P11" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>20</v>
-      </c>
-      <c r="R11" t="n">
-        <v>25</v>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>2058980846</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/2058980846</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
         <is>
           <t>2026-04-28</t>
         </is>

--- a/naver-place-crawler/results_health/제주_PT.xlsx
+++ b/naver-place-crawler/results_health/제주_PT.xlsx
@@ -417,12 +417,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V10"/>
+  <dimension ref="A1:V11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="27" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="29" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
@@ -564,29 +564,29 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>사람휘트니스 이도7호점</t>
+          <t>정글짐 구남점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>saram_ido@naver.com</t>
+          <t>junglegyminherfit@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1404-1264</t>
+          <t>0507-1380-2950</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>제주 제주시 연삼로 424</t>
+          <t>제주 제주시 구남동8길 58 올레마트 2층 정글짐</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/saram_ido</t>
+          <t>https://blog.naver.com/junglegyminherfit</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -606,14 +606,10 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5yc0j</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>X</t>
@@ -621,17 +617,17 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>273</v>
+        <v>126</v>
       </c>
       <c r="Q2" t="n">
-        <v>461</v>
+        <v>85</v>
       </c>
       <c r="R2" t="n">
-        <v>734</v>
+        <v>211</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -640,51 +636,51 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1089331988</t>
+          <t>1471742099</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1089331988</t>
+          <t>https://m.place.naver.com/place/1471742099</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>커스텀짐 한림점</t>
+          <t>마인드휘트니스 중앙점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>customhallim@naver.com</t>
+          <t>mindfitness23@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1363-2448</t>
+          <t>0507-1468-2371</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>제주 제주시 한림읍 한림중앙로 61-14</t>
+          <t>제주 제주시 중앙로 53 JJ아트뷰타워 3, 4층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/custom_hallim/</t>
+          <t>https://blog.naver.com/mindfitness23</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -699,7 +695,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -709,7 +705,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w40eab</t>
+          <t>https://talk.naver.com/ct/wo03pkw</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -723,13 +719,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>753</v>
+        <v>1538</v>
       </c>
       <c r="Q3" t="n">
-        <v>169</v>
+        <v>541</v>
       </c>
       <c r="R3" t="n">
-        <v>922</v>
+        <v>2079</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -738,51 +734,51 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1674334378</t>
+          <t>1840405943</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1674334378</t>
+          <t>https://m.place.naver.com/place/1840405943</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>마인드휘트니스 제주공항점</t>
+          <t>커스텀짐 한림점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>mindfitness13@naver.com</t>
+          <t>customhallim@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1348-0798</t>
+          <t>0507-1363-2448</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>제주 제주시 도령로 167 에이동 2층, 3층</t>
+          <t>제주 제주시 한림읍 한림중앙로 61-14</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/mindfitness13</t>
+          <t>https://www.instagram.com/custom_hallim/</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -797,7 +793,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -807,7 +803,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4ptgx</t>
+          <t>https://talk.naver.com/ct/w40eab</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -821,13 +817,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>2153</v>
+        <v>753</v>
       </c>
       <c r="Q4" t="n">
-        <v>507</v>
+        <v>169</v>
       </c>
       <c r="R4" t="n">
-        <v>2660</v>
+        <v>922</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -836,51 +832,51 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1102972683</t>
+          <t>1674334378</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1102972683</t>
+          <t>https://m.place.naver.com/place/1674334378</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>아틀라스&amp;바른자세 운동센터</t>
+          <t>마인드휘트니스 제주공항점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>atlascs@naver.com</t>
+          <t>mindfitness13@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1341-0145</t>
+          <t>0507-1348-0798</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>제주 제주시 과천로 31 4층</t>
+          <t>제주 제주시 도령로 167 에이동 2층, 3층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/jejuatlas/</t>
+          <t>https://blog.naver.com/mindfitness13</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -895,7 +891,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -905,7 +901,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wcfqcj</t>
+          <t>https://talk.naver.com/ct/w4ptgx</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -919,13 +915,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>129</v>
+        <v>2153</v>
       </c>
       <c r="Q5" t="n">
-        <v>188</v>
+        <v>507</v>
       </c>
       <c r="R5" t="n">
-        <v>317</v>
+        <v>2660</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -934,17 +930,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>37264400</t>
+          <t>1102972683</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37264400</t>
+          <t>https://m.place.naver.com/place/1102972683</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -956,29 +952,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>코어스포츠제주 헬스&amp;PT</t>
+          <t>아틀라스&amp;바른자세 운동센터</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>core_sport_jeju@naver.com</t>
+          <t>atlascs@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1409-1645</t>
+          <t>0507-1341-0145</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>제주 제주시 도령로 64 3층</t>
+          <t>제주 제주시 과천로 31 4층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>http://coresportsjeju.com/</t>
+          <t>https://www.instagram.com/jejuatlas/</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1003,7 +999,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wrehaip</t>
+          <t>https://talk.naver.com/ct/wcfqcj</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1017,13 +1013,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>158</v>
+        <v>129</v>
       </c>
       <c r="Q6" t="n">
-        <v>567</v>
+        <v>188</v>
       </c>
       <c r="R6" t="n">
-        <v>725</v>
+        <v>317</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1032,17 +1028,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1159226809</t>
+          <t>37264400</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1159226809</t>
+          <t>https://m.place.naver.com/place/37264400</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1054,34 +1050,34 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>무브멘탈랩 &amp; 뉴로필라테스</t>
+          <t>코어스포츠제주 헬스&amp;PT</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>move_9@naver.com</t>
+          <t>core_sport_jeju@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1341-2075</t>
+          <t>0507-1409-1645</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>제주 서귀포시 성산읍 일주동로4120번길 23-20 신관 2층, 무브멘탈랩 트레이닝센터</t>
+          <t>제주 제주시 도령로 64 3층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://linktr.ee/jeju_neuro</t>
+          <t>http://coresportsjeju.com/</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1096,10 +1092,14 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wrehaip</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1111,13 +1111,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>85</v>
+        <v>158</v>
       </c>
       <c r="Q7" t="n">
-        <v>94</v>
+        <v>567</v>
       </c>
       <c r="R7" t="n">
-        <v>179</v>
+        <v>725</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1126,51 +1126,51 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1037944274</t>
+          <t>1159226809</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1037944274</t>
+          <t>https://m.place.naver.com/place/1159226809</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>마인드휘트니스 PT&amp;필라테스&amp;요가 동홍점</t>
+          <t>무브멘탈랩 &amp; 뉴로필라테스</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>mindfitness7@naver.com</t>
+          <t>move_9@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1352-0797</t>
+          <t>0507-1341-2075</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>제주 서귀포시 동홍중앙로 55 2층,3층</t>
+          <t>제주 서귀포시 성산읍 일주동로4120번길 23-20 신관 2층, 무브멘탈랩 트레이닝센터</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/mindfitness7</t>
+          <t>https://linktr.ee/jeju_neuro</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1190,14 +1190,10 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4yf5p</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
           <t>X</t>
@@ -1209,13 +1205,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>741</v>
+        <v>85</v>
       </c>
       <c r="Q8" t="n">
-        <v>768</v>
+        <v>94</v>
       </c>
       <c r="R8" t="n">
-        <v>1509</v>
+        <v>179</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1224,17 +1220,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1069617460</t>
+          <t>1037944274</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1069617460</t>
+          <t>https://m.place.naver.com/place/1037944274</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1246,29 +1242,25 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>마인드휘트니스 PT&amp;필라테스&amp;요가 서홍점</t>
+          <t>유제이 PT&amp;필라테스 노형점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>mindfitness2@naver.com</t>
+          <t>ohssang988@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0507-1446-0790</t>
-        </is>
-      </c>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>제주 서귀포시 홍중로 99 2, 3, 4층</t>
+          <t>제주 제주시 남녕로 25 리안스테이노형 3층 302호</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.mindfitness-official.com/</t>
+          <t>https://www.instagram.com/uj_pt0125</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1293,7 +1285,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w47xu3</t>
+          <t>https://talk.naver.com/ct/wn4n9ww</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1307,13 +1299,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1016</v>
+        <v>175</v>
       </c>
       <c r="Q9" t="n">
-        <v>445</v>
+        <v>140</v>
       </c>
       <c r="R9" t="n">
-        <v>1461</v>
+        <v>315</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1322,17 +1314,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1647569204</t>
+          <t>1722027239</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1647569204</t>
+          <t>https://m.place.naver.com/place/1722027239</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1344,29 +1336,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>마인드휘트니스 중앙점</t>
+          <t>리셋 중문점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>mindfitness23@naver.com</t>
+          <t>reset_jungmun@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1468-2371</t>
+          <t>0507-1393-1529</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>제주 제주시 중앙로 53 JJ아트뷰타워 3, 4층</t>
+          <t>제주 서귀포시 대포중앙로 6-8 3층 리셋 중문점</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/mindfitness23</t>
+          <t>https://blog.naver.com/reset_jungmun</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1391,7 +1383,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wo03pkw</t>
+          <t>https://talk.naver.com/ct/wliznta</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1405,13 +1397,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1538</v>
+        <v>5</v>
       </c>
       <c r="Q10" t="n">
-        <v>541</v>
+        <v>20</v>
       </c>
       <c r="R10" t="n">
-        <v>2079</v>
+        <v>25</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1420,17 +1412,115 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1840405943</t>
+          <t>2058980846</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1840405943</t>
+          <t>https://m.place.naver.com/place/2058980846</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>트레이닝 스타</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>trainingstar@naver.com</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0507-1325-9817</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>제주 제주시 노형로 353 3층</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/trainingstar</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4dvi3</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>43</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>28</v>
+      </c>
+      <c r="R11" t="n">
+        <v>71</v>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>1875737855</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1875737855</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/제주_PT.xlsx
+++ b/naver-place-crawler/results_health/제주_PT.xlsx
@@ -421,7 +421,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
     <col width="29" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
@@ -658,29 +658,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>마인드휘트니스 중앙점</t>
+          <t>사람휘트니스 이도7호점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>mindfitness23@naver.com</t>
+          <t>saram_ido@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1468-2371</t>
+          <t>0507-1404-1264</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>제주 제주시 중앙로 53 JJ아트뷰타워 3, 4층</t>
+          <t>제주 제주시 연삼로 424</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/mindfitness23</t>
+          <t>https://blog.naver.com/saram_ido</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -705,7 +705,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wo03pkw</t>
+          <t>https://talk.naver.com/ct/w5yc0j</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1538</v>
+        <v>273</v>
       </c>
       <c r="Q3" t="n">
-        <v>541</v>
+        <v>461</v>
       </c>
       <c r="R3" t="n">
-        <v>2079</v>
+        <v>734</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -734,12 +734,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1840405943</t>
+          <t>1089331988</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1840405943</t>
+          <t>https://m.place.naver.com/place/1089331988</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -751,34 +751,34 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>커스텀짐 한림점</t>
+          <t>마인드휘트니스 중앙점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>customhallim@naver.com</t>
+          <t>mindfitness23@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1363-2448</t>
+          <t>0507-1468-2371</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>제주 제주시 한림읍 한림중앙로 61-14</t>
+          <t>제주 제주시 중앙로 53 JJ아트뷰타워 3, 4층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/custom_hallim/</t>
+          <t>https://blog.naver.com/mindfitness23</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -803,7 +803,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w40eab</t>
+          <t>https://talk.naver.com/ct/wo03pkw</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>753</v>
+        <v>1538</v>
       </c>
       <c r="Q4" t="n">
-        <v>169</v>
+        <v>541</v>
       </c>
       <c r="R4" t="n">
-        <v>922</v>
+        <v>2079</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -832,12 +832,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1674334378</t>
+          <t>1840405943</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1674334378</t>
+          <t>https://m.place.naver.com/place/1840405943</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -849,34 +849,34 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>마인드휘트니스 제주공항점</t>
+          <t>커스텀짐 한림점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>mindfitness13@naver.com</t>
+          <t>customhallim@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1348-0798</t>
+          <t>0507-1363-2448</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>제주 제주시 도령로 167 에이동 2층, 3층</t>
+          <t>제주 제주시 한림읍 한림중앙로 61-14</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/mindfitness13</t>
+          <t>https://www.instagram.com/custom_hallim/</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -891,7 +891,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4ptgx</t>
+          <t>https://talk.naver.com/ct/w40eab</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -915,13 +915,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>2153</v>
+        <v>753</v>
       </c>
       <c r="Q5" t="n">
-        <v>507</v>
+        <v>169</v>
       </c>
       <c r="R5" t="n">
-        <v>2660</v>
+        <v>922</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -930,12 +930,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1102972683</t>
+          <t>1674334378</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1102972683</t>
+          <t>https://m.place.naver.com/place/1674334378</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -947,34 +947,34 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>아틀라스&amp;바른자세 운동센터</t>
+          <t>마인드휘트니스 제주공항점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>atlascs@naver.com</t>
+          <t>mindfitness13@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1341-0145</t>
+          <t>0507-1348-0798</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>제주 제주시 과천로 31 4층</t>
+          <t>제주 제주시 도령로 167 에이동 2층, 3층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/jejuatlas/</t>
+          <t>https://blog.naver.com/mindfitness13</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -989,7 +989,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -999,7 +999,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wcfqcj</t>
+          <t>https://talk.naver.com/ct/w4ptgx</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1013,13 +1013,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>129</v>
+        <v>2153</v>
       </c>
       <c r="Q6" t="n">
-        <v>188</v>
+        <v>507</v>
       </c>
       <c r="R6" t="n">
-        <v>317</v>
+        <v>2660</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1028,12 +1028,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>37264400</t>
+          <t>1102972683</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37264400</t>
+          <t>https://m.place.naver.com/place/1102972683</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1050,34 +1050,34 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>코어스포츠제주 헬스&amp;PT</t>
+          <t>아틀라스&amp;바른자세 운동센터</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>core_sport_jeju@naver.com</t>
+          <t>atlascs@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1409-1645</t>
+          <t>0507-1341-0145</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>제주 제주시 도령로 64 3층</t>
+          <t>제주 제주시 과천로 31 4층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>http://coresportsjeju.com/</t>
+          <t>https://www.instagram.com/jejuatlas/</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1087,7 +1087,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1097,7 +1097,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wrehaip</t>
+          <t>https://talk.naver.com/ct/wcfqcj</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1111,13 +1111,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>158</v>
+        <v>129</v>
       </c>
       <c r="Q7" t="n">
-        <v>567</v>
+        <v>188</v>
       </c>
       <c r="R7" t="n">
-        <v>725</v>
+        <v>317</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1126,12 +1126,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1159226809</t>
+          <t>37264400</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1159226809</t>
+          <t>https://m.place.naver.com/place/37264400</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1148,34 +1148,34 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>무브멘탈랩 &amp; 뉴로필라테스</t>
+          <t>코어스포츠제주 헬스&amp;PT</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>move_9@naver.com</t>
+          <t>core_sport_jeju@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1341-2075</t>
+          <t>0507-1409-1645</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>제주 서귀포시 성산읍 일주동로4120번길 23-20 신관 2층, 무브멘탈랩 트레이닝센터</t>
+          <t>제주 제주시 도령로 64 3층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://linktr.ee/jeju_neuro</t>
+          <t>http://coresportsjeju.com/</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1190,10 +1190,14 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wrehaip</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr">
         <is>
           <t>X</t>
@@ -1205,13 +1209,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>85</v>
+        <v>158</v>
       </c>
       <c r="Q8" t="n">
-        <v>94</v>
+        <v>567</v>
       </c>
       <c r="R8" t="n">
-        <v>179</v>
+        <v>725</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1220,12 +1224,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1037944274</t>
+          <t>1159226809</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1037944274</t>
+          <t>https://m.place.naver.com/place/1159226809</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1237,30 +1241,34 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>유제이 PT&amp;필라테스 노형점</t>
+          <t>무브멘탈랩 &amp; 뉴로필라테스</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ohssang988@naver.com</t>
+          <t>move_9@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0507-1341-2075</t>
+        </is>
+      </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>제주 제주시 남녕로 25 리안스테이노형 3층 302호</t>
+          <t>제주 서귀포시 성산읍 일주동로4120번길 23-20 신관 2층, 무브멘탈랩 트레이닝센터</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/uj_pt0125</t>
+          <t>https://linktr.ee/jeju_neuro</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1275,19 +1283,15 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wn4n9ww</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
           <t>X</t>
@@ -1299,13 +1303,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>175</v>
+        <v>85</v>
       </c>
       <c r="Q9" t="n">
-        <v>140</v>
+        <v>94</v>
       </c>
       <c r="R9" t="n">
-        <v>315</v>
+        <v>179</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1314,12 +1318,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1722027239</t>
+          <t>1037944274</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1722027239</t>
+          <t>https://m.place.naver.com/place/1037944274</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1336,29 +1340,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>리셋 중문점</t>
+          <t>마인드휘트니스 PT&amp;필라테스&amp;요가 동홍점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>reset_jungmun@naver.com</t>
+          <t>mindfitness7@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1393-1529</t>
+          <t>0507-1352-0797</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>제주 서귀포시 대포중앙로 6-8 3층 리셋 중문점</t>
+          <t>제주 서귀포시 동홍중앙로 55 2층,3층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/reset_jungmun</t>
+          <t>https://blog.naver.com/mindfitness7</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1383,7 +1387,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wliznta</t>
+          <t>https://talk.naver.com/ct/w4yf5p</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1397,13 +1401,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>5</v>
+        <v>741</v>
       </c>
       <c r="Q10" t="n">
-        <v>20</v>
+        <v>768</v>
       </c>
       <c r="R10" t="n">
-        <v>25</v>
+        <v>1509</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1412,12 +1416,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2058980846</t>
+          <t>1069617460</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2058980846</t>
+          <t>https://m.place.naver.com/place/1069617460</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1429,44 +1433,44 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>트레이닝 스타</t>
+          <t>마인드휘트니스 PT&amp;필라테스&amp;요가 서홍점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>trainingstar@naver.com</t>
+          <t>mindfitness2@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1325-9817</t>
+          <t>0507-1446-0790</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>제주 제주시 노형로 353 3층</t>
+          <t>제주 서귀포시 홍중로 99 2, 3, 4층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/trainingstar</t>
+          <t>https://www.mindfitness-official.com/</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1481,12 +1485,12 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4dvi3</t>
+          <t>https://talk.naver.com/ct/w47xu3</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1495,13 +1499,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>43</v>
+        <v>1016</v>
       </c>
       <c r="Q11" t="n">
-        <v>28</v>
+        <v>445</v>
       </c>
       <c r="R11" t="n">
-        <v>71</v>
+        <v>1461</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1510,12 +1514,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1875737855</t>
+          <t>1647569204</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1875737855</t>
+          <t>https://m.place.naver.com/place/1647569204</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
